--- a/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-icdo3-transitions-2019.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-icdo3-transitions-2019.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="238">
   <si>
     <t>Property</t>
   </si>
@@ -145,6 +145,18 @@
   </si>
   <si>
     <t>Glukagonom</t>
+  </si>
+  <si>
+    <t>8153/1</t>
+  </si>
+  <si>
+    <t>Gastrinom o.n.A.</t>
+  </si>
+  <si>
+    <t>8153/3</t>
+  </si>
+  <si>
+    <t>Malignes Gastrinom</t>
   </si>
   <si>
     <t>8156/1</t>
@@ -988,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1251,67 +1263,67 @@
         <v>88</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="C17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D17" t="s" s="2">
+      <c r="E17" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D18" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D19" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>98</v>
       </c>
     </row>
     <row r="20">
@@ -1328,24 +1340,24 @@
         <v>101</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D21" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>105</v>
       </c>
     </row>
     <row r="22">
@@ -1362,58 +1374,58 @@
         <v>108</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D23" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D24" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D25" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>118</v>
       </c>
     </row>
     <row r="26">
@@ -1444,27 +1456,27 @@
         <v>38</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="B28" t="s" s="2">
+      <c r="E28" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>128</v>
       </c>
     </row>
     <row r="29">
@@ -1549,41 +1561,41 @@
         <v>147</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D34" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>149</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D35" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E35" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>154</v>
       </c>
     </row>
     <row r="36">
@@ -1682,27 +1694,27 @@
         <v>38</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43">
@@ -1713,24 +1725,24 @@
         <v>182</v>
       </c>
       <c r="C43" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D43" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="D43" t="s" s="2">
+      <c r="E43" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="B44" t="s" s="2">
+      <c r="C44" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>188</v>
@@ -1747,30 +1759,30 @@
         <v>191</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="D46" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="B46" t="s" s="2">
+      <c r="E46" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="47">
@@ -1781,7 +1793,7 @@
         <v>197</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>198</v>
@@ -1798,7 +1810,7 @@
         <v>201</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>202</v>
@@ -1815,7 +1827,7 @@
         <v>205</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>206</v>
@@ -1832,27 +1844,27 @@
         <v>209</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="D51" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="E51" t="s" s="2">
         <v>211</v>
@@ -1860,16 +1872,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E52" t="s" s="2">
         <v>215</v>
@@ -1877,30 +1889,30 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>220</v>
@@ -1911,30 +1923,30 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>226</v>
@@ -1951,7 +1963,7 @@
         <v>229</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>230</v>
@@ -1962,19 +1974,36 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D58" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="E58" t="s" s="2">
+      <c r="B59" t="s" s="2">
         <v>233</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
